--- a/artfynd/A 51928-2024 artfynd.xlsx
+++ b/artfynd/A 51928-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82878421</v>
+        <v>82878398</v>
       </c>
       <c r="B2" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,25 +686,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6439</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -718,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467071.1027279688</v>
+        <v>467071</v>
       </c>
       <c r="R2" t="n">
-        <v>6666326.323956954</v>
+        <v>6666326</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +754,9 @@
           <t>2020-03-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-03-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -816,37 +809,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>82878398</v>
+        <v>82878396</v>
       </c>
       <c r="B3" t="n">
-        <v>73680</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -867,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467071.1027279688</v>
+        <v>467071</v>
       </c>
       <c r="R3" t="n">
-        <v>6666326.323956954</v>
+        <v>6666326</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,19 +888,9 @@
           <t>2020-03-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-03-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -968,12 +946,7 @@
         <v>82878573</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,10 +981,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467071.1027279688</v>
+        <v>467071</v>
       </c>
       <c r="R4" t="n">
-        <v>6666326.323956954</v>
+        <v>6666326</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1041,19 +1014,9 @@
           <t>2020-03-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-03-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1106,49 +1069,36 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>82878396</v>
+        <v>82878421</v>
       </c>
       <c r="B5" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1157,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467071.1027279688</v>
+        <v>467071</v>
       </c>
       <c r="R5" t="n">
-        <v>6666326.323956954</v>
+        <v>6666326</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1190,19 +1140,9 @@
           <t>2020-03-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-03-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
